--- a/mapping/Fungi.xlsx
+++ b/mapping/Fungi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1364,6 +1364,114 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Thermoascus</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>嗜热子囊菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ogataea</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>小笠原酵母属</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Nakaseomyces</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>中濑氏酵母属</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cercospora</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>尾孢属</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Trichosporon</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>毛孢子菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Neurospora</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>脉孢菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Wallemia</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>瓦雷迈菌属</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Coniosporium</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>锥孢霉属</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Paraphaeosphaeria</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>拟暗球腔菌属</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
